--- a/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_18-09-2026.xlsx
+++ b/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_18-09-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Ecotherm_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF1F5A4-5F95-47EA-ACA1-B11A8225B2F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B75B70B-AE7B-4095-8673-CC477183866D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30165" yWindow="1365" windowWidth="21600" windowHeight="12510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32520" yWindow="1080" windowWidth="21600" windowHeight="12510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -91,40 +91,46 @@
     <t>N/L</t>
   </si>
   <si>
+    <t>£12.85</t>
+  </si>
+  <si>
+    <t>£16.75</t>
+  </si>
+  <si>
+    <t>£31.22</t>
+  </si>
+  <si>
+    <t>£14.39</t>
+  </si>
+  <si>
+    <t>Add to Enquiry</t>
+  </si>
+  <si>
+    <t>Timeout</t>
+  </si>
+  <si>
+    <t>ET30mm</t>
+  </si>
+  <si>
+    <t>30mm EcoTherm Eco-versal Insulation Board</t>
+  </si>
+  <si>
+    <t>£16.99</t>
+  </si>
+  <si>
+    <t>£16.70</t>
+  </si>
+  <si>
+    <t>£26.51</t>
+  </si>
+  <si>
+    <t>£25.38</t>
+  </si>
+  <si>
     <t>£15.65</t>
   </si>
   <si>
-    <t>£31.22</t>
-  </si>
-  <si>
-    <t>£14.39</t>
-  </si>
-  <si>
-    <t>Add to Enquiry</t>
-  </si>
-  <si>
-    <t>£15.19</t>
-  </si>
-  <si>
-    <t>ET30mm</t>
-  </si>
-  <si>
-    <t>30mm EcoTherm Eco-versal Insulation Board</t>
-  </si>
-  <si>
-    <t>£16.99</t>
-  </si>
-  <si>
-    <t>£16.70</t>
-  </si>
-  <si>
-    <t>£26.51</t>
-  </si>
-  <si>
-    <t>£25.38</t>
-  </si>
-  <si>
-    <t>£19.01</t>
+    <t>£19.50</t>
   </si>
   <si>
     <t>£36.19</t>
@@ -154,7 +160,10 @@
     <t>£29.54</t>
   </si>
   <si>
-    <t>£22.90</t>
+    <t>£18.79</t>
+  </si>
+  <si>
+    <t>£22.78</t>
   </si>
   <si>
     <t>£40.21</t>
@@ -181,7 +190,10 @@
     <t>£33.09</t>
   </si>
   <si>
-    <t>£24.55</t>
+    <t>£20.25</t>
+  </si>
+  <si>
+    <t>£24.35</t>
   </si>
   <si>
     <t>£47.6</t>
@@ -208,7 +220,7 @@
     <t>£38.24</t>
   </si>
   <si>
-    <t>£30.70</t>
+    <t>£25.20</t>
   </si>
   <si>
     <t>£55.16</t>
@@ -238,7 +250,7 @@
     <t>£40.79</t>
   </si>
   <si>
-    <t>£34.62</t>
+    <t>£28.43</t>
   </si>
   <si>
     <t>£60.62</t>
@@ -262,7 +274,7 @@
     <t>£41.02</t>
   </si>
   <si>
-    <t>£33.60</t>
+    <t>£27.63</t>
   </si>
   <si>
     <t>£65.74</t>
@@ -289,7 +301,7 @@
     <t>£44.91</t>
   </si>
   <si>
-    <t>£39.16</t>
+    <t>£31.36</t>
   </si>
   <si>
     <t>£57.8</t>
@@ -313,7 +325,7 @@
     <t>£50.07</t>
   </si>
   <si>
-    <t>£42.21</t>
+    <t>£34.65</t>
   </si>
   <si>
     <t>£67.72</t>
@@ -340,7 +352,7 @@
     <t>£51.51</t>
   </si>
   <si>
-    <t>£41.68</t>
+    <t>£34.97</t>
   </si>
   <si>
     <t>£68.88</t>
@@ -391,7 +403,7 @@
     <t>£59.94</t>
   </si>
   <si>
-    <t>£52.70</t>
+    <t>£43.18</t>
   </si>
   <si>
     <t>£81.19</t>
@@ -415,7 +427,7 @@
     <t>£67.14</t>
   </si>
   <si>
-    <t>£59.85</t>
+    <t>£49.15</t>
   </si>
   <si>
     <t>£81.73</t>
@@ -442,7 +454,7 @@
     <t>£62.82</t>
   </si>
   <si>
-    <t>£64.58</t>
+    <t>£51.82</t>
   </si>
   <si>
     <t>£92.53</t>
@@ -466,7 +478,7 @@
     <t>£72.97</t>
   </si>
   <si>
-    <t>£63.36</t>
+    <t>£52.04</t>
   </si>
   <si>
     <t>£95.89</t>
@@ -475,6 +487,39 @@
     <t>£60.22</t>
   </si>
   <si>
+    <t>£29.63</t>
+  </si>
+  <si>
+    <t>£35.00</t>
+  </si>
+  <si>
+    <t>£34.82</t>
+  </si>
+  <si>
+    <t>£38.53</t>
+  </si>
+  <si>
+    <t>£41.35</t>
+  </si>
+  <si>
+    <t>£42.14</t>
+  </si>
+  <si>
+    <t>£51.19</t>
+  </si>
+  <si>
+    <t>£49.01</t>
+  </si>
+  <si>
+    <t>£59.35</t>
+  </si>
+  <si>
+    <t>£60.38</t>
+  </si>
+  <si>
+    <t>£75.21</t>
+  </si>
+  <si>
     <t>£15.00</t>
   </si>
   <si>
@@ -512,51 +557,6 @@
   </si>
   <si>
     <t>£62.50</t>
-  </si>
-  <si>
-    <t>£16.75</t>
-  </si>
-  <si>
-    <t>£19.50</t>
-  </si>
-  <si>
-    <t>£22.78</t>
-  </si>
-  <si>
-    <t>£24.35</t>
-  </si>
-  <si>
-    <t>£29.63</t>
-  </si>
-  <si>
-    <t>£35.00</t>
-  </si>
-  <si>
-    <t>£34.82</t>
-  </si>
-  <si>
-    <t>£38.53</t>
-  </si>
-  <si>
-    <t>£41.35</t>
-  </si>
-  <si>
-    <t>£42.14</t>
-  </si>
-  <si>
-    <t>£51.19</t>
-  </si>
-  <si>
-    <t>£49.01</t>
-  </si>
-  <si>
-    <t>£59.35</t>
-  </si>
-  <si>
-    <t>£60.38</t>
-  </si>
-  <si>
-    <t>£75.21</t>
   </si>
 </sst>
 </file>
@@ -998,7 +998,7 @@
         <v>21</v>
       </c>
       <c r="I2" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="J2" t="s">
         <v>22</v>
@@ -1007,477 +1007,477 @@
         <v>23</v>
       </c>
       <c r="L2" t="s">
-        <v>164</v>
+        <v>24</v>
       </c>
       <c r="M2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I3" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="J3" t="s">
         <v>22</v>
       </c>
       <c r="K3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L3" t="s">
-        <v>165</v>
+        <v>36</v>
       </c>
       <c r="M3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4" t="s">
+        <v>168</v>
+      </c>
+      <c r="J4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" t="s">
+        <v>46</v>
+      </c>
+      <c r="L4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M4" t="s">
+        <v>48</v>
+      </c>
+      <c r="N4" t="s">
         <v>42</v>
       </c>
-      <c r="H4" t="s">
-        <v>43</v>
-      </c>
-      <c r="I4" t="s">
-        <v>153</v>
-      </c>
-      <c r="J4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K4" t="s">
-        <v>44</v>
-      </c>
-      <c r="L4" t="s">
-        <v>166</v>
-      </c>
-      <c r="M4" t="s">
-        <v>45</v>
-      </c>
-      <c r="N4" t="s">
-        <v>40</v>
-      </c>
       <c r="O4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" t="s">
+        <v>169</v>
+      </c>
+      <c r="J5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" t="s">
+        <v>56</v>
+      </c>
+      <c r="L5" t="s">
+        <v>57</v>
+      </c>
+      <c r="M5" t="s">
+        <v>58</v>
+      </c>
+      <c r="N5" t="s">
         <v>52</v>
       </c>
-      <c r="I5" t="s">
-        <v>154</v>
-      </c>
-      <c r="J5" t="s">
-        <v>22</v>
-      </c>
-      <c r="K5" t="s">
-        <v>53</v>
-      </c>
-      <c r="L5" t="s">
-        <v>167</v>
-      </c>
-      <c r="M5" t="s">
-        <v>54</v>
-      </c>
-      <c r="N5" t="s">
-        <v>49</v>
-      </c>
       <c r="O5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P5" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E6" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H6" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="I6" t="s">
+        <v>170</v>
+      </c>
+      <c r="J6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" t="s">
+        <v>66</v>
+      </c>
+      <c r="L6" t="s">
         <v>155</v>
       </c>
-      <c r="J6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K6" t="s">
-        <v>62</v>
-      </c>
-      <c r="L6" t="s">
-        <v>168</v>
-      </c>
       <c r="M6" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="N6" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="O6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P6" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E7" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F7" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G7" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H7" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I7" t="s">
+        <v>171</v>
+      </c>
+      <c r="J7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L7" t="s">
         <v>156</v>
       </c>
-      <c r="J7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K7" t="s">
+      <c r="M7" t="s">
+        <v>77</v>
+      </c>
+      <c r="N7" t="s">
         <v>72</v>
       </c>
-      <c r="L7" t="s">
-        <v>169</v>
-      </c>
-      <c r="M7" t="s">
-        <v>73</v>
-      </c>
-      <c r="N7" t="s">
-        <v>68</v>
-      </c>
       <c r="O7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P7" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E8" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F8" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G8" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H8" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I8" t="s">
+        <v>172</v>
+      </c>
+      <c r="J8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L8" t="s">
         <v>157</v>
       </c>
-      <c r="J8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K8" t="s">
-        <v>80</v>
-      </c>
-      <c r="L8" t="s">
-        <v>170</v>
-      </c>
       <c r="M8" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="N8" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="O8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P8" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E9" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F9" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G9" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="H9" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="I9" t="s">
+        <v>173</v>
+      </c>
+      <c r="J9" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" t="s">
+        <v>93</v>
+      </c>
+      <c r="L9" t="s">
         <v>158</v>
       </c>
-      <c r="J9" t="s">
-        <v>22</v>
-      </c>
-      <c r="K9" t="s">
+      <c r="M9" t="s">
+        <v>94</v>
+      </c>
+      <c r="N9" t="s">
         <v>89</v>
       </c>
-      <c r="L9" t="s">
-        <v>171</v>
-      </c>
-      <c r="M9" t="s">
-        <v>90</v>
-      </c>
-      <c r="N9" t="s">
-        <v>85</v>
-      </c>
       <c r="O9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P9" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E10" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F10" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G10" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="H10" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I10" t="s">
+        <v>174</v>
+      </c>
+      <c r="J10" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10" t="s">
+        <v>101</v>
+      </c>
+      <c r="L10" t="s">
         <v>159</v>
       </c>
-      <c r="J10" t="s">
-        <v>22</v>
-      </c>
-      <c r="K10" t="s">
-        <v>97</v>
-      </c>
-      <c r="L10" t="s">
-        <v>172</v>
-      </c>
       <c r="M10" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="N10" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="O10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P10" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B11" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E11" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F11" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G11" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="H11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="I11" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="J11" t="s">
         <v>22</v>
       </c>
       <c r="K11" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="L11" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="M11" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="N11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="O11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P11" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B12" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C12" t="s">
         <v>22</v>
@@ -1492,13 +1492,13 @@
         <v>22</v>
       </c>
       <c r="G12" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H12" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I12" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="J12" t="s">
         <v>22</v>
@@ -1507,219 +1507,219 @@
         <v>22</v>
       </c>
       <c r="L12" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="M12" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="N12" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="O12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P12" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B13" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C13" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D13" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E13" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F13" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G13" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="I13" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="J13" t="s">
         <v>22</v>
       </c>
       <c r="K13" t="s">
+        <v>127</v>
+      </c>
+      <c r="L13" t="s">
+        <v>162</v>
+      </c>
+      <c r="M13" t="s">
+        <v>128</v>
+      </c>
+      <c r="N13" t="s">
         <v>123</v>
       </c>
-      <c r="L13" t="s">
-        <v>175</v>
-      </c>
-      <c r="M13" t="s">
-        <v>124</v>
-      </c>
-      <c r="N13" t="s">
-        <v>119</v>
-      </c>
       <c r="O13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P13" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B14" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C14" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D14" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E14" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F14" t="s">
         <v>22</v>
       </c>
       <c r="G14" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="H14" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="I14" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="J14" t="s">
         <v>22</v>
       </c>
       <c r="K14" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="L14" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="M14" t="s">
+        <v>136</v>
+      </c>
+      <c r="N14" t="s">
         <v>132</v>
       </c>
-      <c r="N14" t="s">
-        <v>128</v>
-      </c>
       <c r="O14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P14" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B15" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C15" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D15" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E15" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="F15" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G15" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="H15" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="I15" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="J15" t="s">
         <v>22</v>
       </c>
       <c r="K15" t="s">
+        <v>144</v>
+      </c>
+      <c r="L15" t="s">
+        <v>164</v>
+      </c>
+      <c r="M15" t="s">
+        <v>145</v>
+      </c>
+      <c r="N15" t="s">
         <v>140</v>
       </c>
-      <c r="L15" t="s">
-        <v>177</v>
-      </c>
-      <c r="M15" t="s">
-        <v>141</v>
-      </c>
-      <c r="N15" t="s">
-        <v>136</v>
-      </c>
       <c r="O15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P15" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B16" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C16" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D16" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E16" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F16" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="G16" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="H16" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I16" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="J16" t="s">
         <v>22</v>
       </c>
       <c r="K16" t="s">
+        <v>152</v>
+      </c>
+      <c r="L16" t="s">
+        <v>165</v>
+      </c>
+      <c r="M16" t="s">
+        <v>153</v>
+      </c>
+      <c r="N16" t="s">
         <v>148</v>
       </c>
-      <c r="L16" t="s">
-        <v>178</v>
-      </c>
-      <c r="M16" t="s">
-        <v>149</v>
-      </c>
-      <c r="N16" t="s">
-        <v>144</v>
-      </c>
       <c r="O16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P16" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
